--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="100">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,66 +505,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -580,298 +585,298 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from unknown" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="236">
   <si>
     <t>Property</t>
   </si>
@@ -30,21 +31,18 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>VSVFVitalsBodySite</t>
+    <t>VF_VitalsBodySite</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>VF_VitalsBodySite</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +311,418 @@
   </si>
   <si>
     <t>urn:undefined</t>
+  </si>
+  <si>
+    <t>818983003</t>
+  </si>
+  <si>
+    <t>Abdomen (body structure)</t>
+  </si>
+  <si>
+    <t>344001</t>
+  </si>
+  <si>
+    <t>Ankle region structure (body structure)</t>
+  </si>
+  <si>
+    <t>51636004</t>
+  </si>
+  <si>
+    <t>Structure of left ankle (body structure)</t>
+  </si>
+  <si>
+    <t>6685009</t>
+  </si>
+  <si>
+    <t>Structure of right ankle (body structure)</t>
+  </si>
+  <si>
+    <t>46707002</t>
+  </si>
+  <si>
+    <t>Structure of precordium (body structure)</t>
+  </si>
+  <si>
+    <t>128617001</t>
+  </si>
+  <si>
+    <t>Arteriovenous fistula (morphologic abnormality)</t>
+  </si>
+  <si>
+    <t>422543003</t>
+  </si>
+  <si>
+    <t>Structure of axillary fossa (body structure)</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>764473004 |Skin structure of left axilla (body structure)|
+20437008 |Structure of left axillary region (body structure)|</t>
+  </si>
+  <si>
+    <t>54718008</t>
+  </si>
+  <si>
+    <t>Peripheral pulse, function (observable entity)</t>
+  </si>
+  <si>
+    <t>17137000</t>
+  </si>
+  <si>
+    <t>Structure of brachial artery (body structure)</t>
+  </si>
+  <si>
+    <t>723961002</t>
+  </si>
+  <si>
+    <t>Structure of left brachial artery (body structure)</t>
+  </si>
+  <si>
+    <t>723962009</t>
+  </si>
+  <si>
+    <t>Structure of right brachial artery (body structure)</t>
+  </si>
+  <si>
+    <t>53840002</t>
+  </si>
+  <si>
+    <t>Structure of calf of leg (body structure)</t>
+  </si>
+  <si>
+    <t>722115008</t>
+  </si>
+  <si>
+    <t>Structure of calf of left lower leg (body structure)</t>
+  </si>
+  <si>
+    <t>722116009</t>
+  </si>
+  <si>
+    <t>Structure of calf of right lower leg (body structure)</t>
+  </si>
+  <si>
+    <t>69105007</t>
+  </si>
+  <si>
+    <t>Carotid artery structure (body structure)</t>
+  </si>
+  <si>
+    <t>721028001</t>
+  </si>
+  <si>
+    <t>Structure of left carotid artery (body structure)</t>
+  </si>
+  <si>
+    <t>721033002</t>
+  </si>
+  <si>
+    <t>Structure of right carotid artery (body structure)</t>
+  </si>
+  <si>
+    <t>276885007</t>
+  </si>
+  <si>
+    <t>Core body temperature (observable entity)</t>
+  </si>
+  <si>
+    <t>86547008</t>
+  </si>
+  <si>
+    <t>Structure of dorsalis pedis artery (body structure)</t>
+  </si>
+  <si>
+    <t>792817008</t>
+  </si>
+  <si>
+    <t>Structure of left dorsalis pedis artery (body structure)</t>
+  </si>
+  <si>
+    <t>792816004</t>
+  </si>
+  <si>
+    <t>Structure of right dorsalis pedis artery (body structure)</t>
+  </si>
+  <si>
+    <t>7657000</t>
+  </si>
+  <si>
+    <t>Structure of femoral artery (body structure)</t>
+  </si>
+  <si>
+    <t>113270003</t>
+  </si>
+  <si>
+    <t>Structure of left femoral artery (body structure)</t>
+  </si>
+  <si>
+    <t>69833005</t>
+  </si>
+  <si>
+    <t>Structure of right femoral artery (body structure)</t>
+  </si>
+  <si>
+    <t>69536005</t>
+  </si>
+  <si>
+    <t>Head structure (body structure)</t>
+  </si>
+  <si>
+    <t>29836001</t>
+  </si>
+  <si>
+    <t>Hip region structure (body structure)</t>
+  </si>
+  <si>
+    <t>287679003</t>
+  </si>
+  <si>
+    <t>Left hip region structure (body structure)</t>
+  </si>
+  <si>
+    <t>287579007</t>
+  </si>
+  <si>
+    <t>Right hip region structure (body structure)</t>
+  </si>
+  <si>
+    <t>72696002</t>
+  </si>
+  <si>
+    <t>Knee region structure (body structure)</t>
+  </si>
+  <si>
+    <t>82169009</t>
+  </si>
+  <si>
+    <t>Structure of left knee region (body structure)</t>
+  </si>
+  <si>
+    <t>6757004</t>
+  </si>
+  <si>
+    <t>Structure of right knee region (body structure)</t>
+  </si>
+  <si>
+    <t>80768000</t>
+  </si>
+  <si>
+    <t>Structure of left upper limb (body structure)</t>
+  </si>
+  <si>
+    <t>32153003</t>
+  </si>
+  <si>
+    <t>Structure of left lower limb (body structure)</t>
+  </si>
+  <si>
+    <t>14975008</t>
+  </si>
+  <si>
+    <t>Forearm structure (body structure)</t>
+  </si>
+  <si>
+    <t>66480008</t>
+  </si>
+  <si>
+    <t>Structure of left forearm (body structure)</t>
+  </si>
+  <si>
+    <t>64262003</t>
+  </si>
+  <si>
+    <t>Structure of right forearm (body structure)</t>
+  </si>
+  <si>
+    <t>45048000</t>
+  </si>
+  <si>
+    <t>Neck structure (body structure)</t>
+  </si>
+  <si>
+    <t>123851003</t>
+  </si>
+  <si>
+    <t>Mouth region structure (body structure)</t>
+  </si>
+  <si>
+    <t>43899006</t>
+  </si>
+  <si>
+    <t>Structure of popliteal artery (body structure)</t>
+  </si>
+  <si>
+    <t>25885001</t>
+  </si>
+  <si>
+    <t>Left popliteal artery structure (body structure)</t>
+  </si>
+  <si>
+    <t>57832007</t>
+  </si>
+  <si>
+    <t>Structure of right popliteal artery (body structure)</t>
+  </si>
+  <si>
+    <t>13363002</t>
+  </si>
+  <si>
+    <t>Structure of posterior tibial artery (body structure)</t>
+  </si>
+  <si>
+    <t>214912001</t>
+  </si>
+  <si>
+    <t>Structure of left posterior tibial artery (body structure)</t>
+  </si>
+  <si>
+    <t>214811007</t>
+  </si>
+  <si>
+    <t>Structure of right posterior tibial artery (body structure)</t>
+  </si>
+  <si>
+    <t>6921000</t>
+  </si>
+  <si>
+    <t>Structure of right upper limb (body structure)</t>
+  </si>
+  <si>
+    <t>62175007</t>
+  </si>
+  <si>
+    <t>Structure of right lower limb (body structure)</t>
+  </si>
+  <si>
+    <t>45631007</t>
+  </si>
+  <si>
+    <t>Structure of radial artery (body structure)</t>
+  </si>
+  <si>
+    <t>368504007</t>
+  </si>
+  <si>
+    <t>Structure of left radial artery (body structure)</t>
+  </si>
+  <si>
+    <t>368503001</t>
+  </si>
+  <si>
+    <t>Structure of right radial artery (body structure)</t>
+  </si>
+  <si>
+    <t>34402009</t>
+  </si>
+  <si>
+    <t>Rectum structure (body structure)</t>
+  </si>
+  <si>
+    <t>39937001</t>
+  </si>
+  <si>
+    <t>Skin structure (body structure)</t>
+  </si>
+  <si>
+    <t>450721000</t>
+  </si>
+  <si>
+    <t>Structure of temporal region (body structure)</t>
+  </si>
+  <si>
+    <t>68367000</t>
+  </si>
+  <si>
+    <t>Thigh structure (body structure)</t>
+  </si>
+  <si>
+    <t>61396006</t>
+  </si>
+  <si>
+    <t>Structure of left thigh (body structure)</t>
+  </si>
+  <si>
+    <t>11207009</t>
+  </si>
+  <si>
+    <t>Structure of right thigh (body structure)</t>
+  </si>
+  <si>
+    <t>42859004</t>
+  </si>
+  <si>
+    <t>Tympanic membrane structure (body structure)</t>
+  </si>
+  <si>
+    <t>726562006</t>
+  </si>
+  <si>
+    <t>Structure of left tympanic membrane (body structure)</t>
+  </si>
+  <si>
+    <t>726563001</t>
+  </si>
+  <si>
+    <t>Structure of right tympanic membrane (body structure)</t>
+  </si>
+  <si>
+    <t>44984001</t>
+  </si>
+  <si>
+    <t>Structure of ulnar artery (body structure)</t>
+  </si>
+  <si>
+    <t>368506009</t>
+  </si>
+  <si>
+    <t>Structure of left ulnar artery (body structure)</t>
+  </si>
+  <si>
+    <t>368505008</t>
+  </si>
+  <si>
+    <t>Structure of right ulnar artery (body structure)</t>
+  </si>
+  <si>
+    <t>40983000</t>
+  </si>
+  <si>
+    <t>Structure of upper extremity between shoulder and elbow (body structure)</t>
+  </si>
+  <si>
+    <t>368208006</t>
+  </si>
+  <si>
+    <t>Left upper arm structure (body structure)</t>
+  </si>
+  <si>
+    <t>368209003</t>
+  </si>
+  <si>
+    <t>Right upper arm structure (body structure)</t>
+  </si>
+  <si>
+    <t>8205005</t>
+  </si>
+  <si>
+    <t>Wrist region structure (body structure)</t>
+  </si>
+  <si>
+    <t>5951000</t>
+  </si>
+  <si>
+    <t>Structure of left wrist region (body structure)</t>
+  </si>
+  <si>
+    <t>9736006</t>
+  </si>
+  <si>
+    <t>Structure of right wrist region (body structure)</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -490,83 +900,83 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -585,298 +995,880 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>98</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B71"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="B37" t="s" s="2">
-        <v>99</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="233">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,10 +80,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Navigate to [ConceptMap VF_VitalsBodySite](ConceptMap-CMVFVitalsBodySite.html)
-&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -949,28 +945,26 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +983,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -997,554 +991,554 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>103</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>131</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>145</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1563,7 +1557,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -1571,290 +1565,290 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="234">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet for terminology map VF_VitalsBodySite</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -945,26 +948,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +988,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -991,554 +996,554 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1562,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -1565,290 +1570,290 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from unknown" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from US Department of" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for terminology map VF_VitalsBodySite</t>
+    <t>ValueSet for Terminology Maps VF_VitalsBodySite</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -715,7 +715,7 @@
     <t>WRIST</t>
   </si>
   <si>
-    <t>urn:undefined</t>
+    <t>http://terminology.hl7.org/CodeSystem/VHA</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from US Department of" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -52,13 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for Terminology Maps VF_VitalsBodySite</t>
+    <t>FHIR Target ValueSet for Terminology Maps VF_VitalsBodySite</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -509,213 +508,6 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>4688633</t>
-  </si>
-  <si>
-    <t>ABDOMINAL</t>
-  </si>
-  <si>
-    <t>4688636</t>
-  </si>
-  <si>
-    <t>ANKLE</t>
-  </si>
-  <si>
-    <t>4688637</t>
-  </si>
-  <si>
-    <t>APICAL</t>
-  </si>
-  <si>
-    <t>4688696</t>
-  </si>
-  <si>
-    <t>AV FISTULA</t>
-  </si>
-  <si>
-    <t>4688640</t>
-  </si>
-  <si>
-    <t>AXILLARY</t>
-  </si>
-  <si>
-    <t>4688642</t>
-  </si>
-  <si>
-    <t>BILATERAL PERIPHERALS</t>
-  </si>
-  <si>
-    <t>4688643</t>
-  </si>
-  <si>
-    <t>BRACHIAL</t>
-  </si>
-  <si>
-    <t>4688644</t>
-  </si>
-  <si>
-    <t>CALF</t>
-  </si>
-  <si>
-    <t>4688645</t>
-  </si>
-  <si>
-    <t>CAROTID</t>
-  </si>
-  <si>
-    <t>4688648</t>
-  </si>
-  <si>
-    <t>CORE</t>
-  </si>
-  <si>
-    <t>4688651</t>
-  </si>
-  <si>
-    <t>DORSALIS PEDIS</t>
-  </si>
-  <si>
-    <t>4688655</t>
-  </si>
-  <si>
-    <t>FEMORAL</t>
-  </si>
-  <si>
-    <t>4688656</t>
-  </si>
-  <si>
-    <t>HEAD</t>
-  </si>
-  <si>
-    <t>4697470</t>
-  </si>
-  <si>
-    <t>HIP</t>
-  </si>
-  <si>
-    <t>4688689</t>
-  </si>
-  <si>
-    <t>KNEE</t>
-  </si>
-  <si>
-    <t>4688657</t>
-  </si>
-  <si>
-    <t>L ARM (LEFT ARM)</t>
-  </si>
-  <si>
-    <t>4688658</t>
-  </si>
-  <si>
-    <t>L LEG (LEFT LEG)</t>
-  </si>
-  <si>
-    <t>4688662</t>
-  </si>
-  <si>
-    <t>LOWER ARM</t>
-  </si>
-  <si>
-    <t>4688686</t>
-  </si>
-  <si>
-    <t>NECK</t>
-  </si>
-  <si>
-    <t>4500642</t>
-  </si>
-  <si>
-    <t>ORAL</t>
-  </si>
-  <si>
-    <t>4688672</t>
-  </si>
-  <si>
-    <t>PERIPHERAL</t>
-  </si>
-  <si>
-    <t>4688673</t>
-  </si>
-  <si>
-    <t>POPLITEAL</t>
-  </si>
-  <si>
-    <t>4688675</t>
-  </si>
-  <si>
-    <t>POSTERIOR TIBIAL</t>
-  </si>
-  <si>
-    <t>4688676</t>
-  </si>
-  <si>
-    <t>R ARM (RIGHT ARM)</t>
-  </si>
-  <si>
-    <t>4688677</t>
-  </si>
-  <si>
-    <t>R LEG (RIGHT LEG)</t>
-  </si>
-  <si>
-    <t>4688678</t>
-  </si>
-  <si>
-    <t>RADIAL</t>
-  </si>
-  <si>
-    <t>4688679</t>
-  </si>
-  <si>
-    <t>RECTAL</t>
-  </si>
-  <si>
-    <t>4688704</t>
-  </si>
-  <si>
-    <t>SKIN</t>
-  </si>
-  <si>
-    <t>4537028</t>
-  </si>
-  <si>
-    <t>TEMPORAL</t>
-  </si>
-  <si>
-    <t>4688708</t>
-  </si>
-  <si>
-    <t>THIGH</t>
-  </si>
-  <si>
-    <t>4688712</t>
-  </si>
-  <si>
-    <t>TYMPANIC</t>
-  </si>
-  <si>
-    <t>4688713</t>
-  </si>
-  <si>
-    <t>ULNAR</t>
-  </si>
-  <si>
-    <t>4688714</t>
-  </si>
-  <si>
-    <t>UPPER ARM</t>
-  </si>
-  <si>
-    <t>4688717</t>
-  </si>
-  <si>
-    <t>WRIST</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/VHA</t>
   </si>
 </sst>
 </file>
@@ -1549,314 +1341,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>233</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOWMED CT" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOWMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="167">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -138,7 +138,194 @@
     <t>422543003</t>
   </si>
   <si>
-    <t>Structure of axillary fossa (body structure)</t>
+    <t>Structure of axillary fossa (body structure)
+76261009 |Skin structure of axilla (body structure)|</t>
+  </si>
+  <si>
+    <t>840581000</t>
+  </si>
+  <si>
+    <t>Structure of peripheral artery (body structure)</t>
+  </si>
+  <si>
+    <t>17137000</t>
+  </si>
+  <si>
+    <t>Structure of brachial artery (body structure)</t>
+  </si>
+  <si>
+    <t>723961002</t>
+  </si>
+  <si>
+    <t>Structure of left brachial artery (body structure)</t>
+  </si>
+  <si>
+    <t>723962009</t>
+  </si>
+  <si>
+    <t>Structure of right brachial artery (body structure)</t>
+  </si>
+  <si>
+    <t>53840002</t>
+  </si>
+  <si>
+    <t>Structure of calf of leg (body structure)</t>
+  </si>
+  <si>
+    <t>722115008</t>
+  </si>
+  <si>
+    <t>Structure of calf of left lower leg (body structure)</t>
+  </si>
+  <si>
+    <t>722116009</t>
+  </si>
+  <si>
+    <t>Structure of calf of right lower leg (body structure)</t>
+  </si>
+  <si>
+    <t>69105007</t>
+  </si>
+  <si>
+    <t>Carotid artery structure (body structure)</t>
+  </si>
+  <si>
+    <t>721028001</t>
+  </si>
+  <si>
+    <t>Structure of left carotid artery (body structure)</t>
+  </si>
+  <si>
+    <t>721033002</t>
+  </si>
+  <si>
+    <t>Structure of right carotid artery (body structure)</t>
+  </si>
+  <si>
+    <t>276885007</t>
+  </si>
+  <si>
+    <t>Core body temperature (observable entity)</t>
+  </si>
+  <si>
+    <t>86547008</t>
+  </si>
+  <si>
+    <t>Structure of dorsalis pedis artery (body structure)</t>
+  </si>
+  <si>
+    <t>792817008</t>
+  </si>
+  <si>
+    <t>Structure of left dorsalis pedis artery (body structure)</t>
+  </si>
+  <si>
+    <t>792816004</t>
+  </si>
+  <si>
+    <t>Structure of right dorsalis pedis artery (body structure)</t>
+  </si>
+  <si>
+    <t>7657000</t>
+  </si>
+  <si>
+    <t>Structure of femoral artery (body structure)</t>
+  </si>
+  <si>
+    <t>113270003</t>
+  </si>
+  <si>
+    <t>Structure of left femoral artery (body structure)</t>
+  </si>
+  <si>
+    <t>69833005</t>
+  </si>
+  <si>
+    <t>Structure of right femoral artery (body structure)</t>
+  </si>
+  <si>
+    <t>69536005</t>
+  </si>
+  <si>
+    <t>Head structure (body structure)</t>
+  </si>
+  <si>
+    <t>29836001</t>
+  </si>
+  <si>
+    <t>Hip region structure (body structure)</t>
+  </si>
+  <si>
+    <t>287679003</t>
+  </si>
+  <si>
+    <t>Left hip region structure (body structure)</t>
+  </si>
+  <si>
+    <t>287579007</t>
+  </si>
+  <si>
+    <t>Right hip region structure (body structure)</t>
+  </si>
+  <si>
+    <t>72696002</t>
+  </si>
+  <si>
+    <t>Knee region structure (body structure)</t>
+  </si>
+  <si>
+    <t>82169009</t>
+  </si>
+  <si>
+    <t>Structure of left knee region (body structure)</t>
+  </si>
+  <si>
+    <t>6757004</t>
+  </si>
+  <si>
+    <t>Structure of right knee region (body structure)</t>
+  </si>
+  <si>
+    <t>80768000</t>
+  </si>
+  <si>
+    <t>Structure of left upper limb (body structure)</t>
+  </si>
+  <si>
+    <t>32153003</t>
+  </si>
+  <si>
+    <t>Structure of left lower limb (body structure)</t>
+  </si>
+  <si>
+    <t>14975008</t>
+  </si>
+  <si>
+    <t>Forearm structure (body structure)</t>
+  </si>
+  <si>
+    <t>66480008</t>
+  </si>
+  <si>
+    <t>Structure of left forearm (body structure)</t>
+  </si>
+  <si>
+    <t>64262003</t>
+  </si>
+  <si>
+    <t>Structure of right forearm (body structure)</t>
+  </si>
+  <si>
+    <t>45048000</t>
+  </si>
+  <si>
+    <t>Neck structure (body structure)</t>
+  </si>
+  <si>
+    <t>123851003</t>
+  </si>
+  <si>
+    <t>Mouth region structure (body structure)</t>
   </si>
   <si>
     <t>54718008</t>
@@ -147,186 +334,6 @@
     <t>Peripheral pulse, function (observable entity)</t>
   </si>
   <si>
-    <t>17137000</t>
-  </si>
-  <si>
-    <t>Structure of brachial artery (body structure)</t>
-  </si>
-  <si>
-    <t>723961002</t>
-  </si>
-  <si>
-    <t>Structure of left brachial artery (body structure)</t>
-  </si>
-  <si>
-    <t>723962009</t>
-  </si>
-  <si>
-    <t>Structure of right brachial artery (body structure)</t>
-  </si>
-  <si>
-    <t>53840002</t>
-  </si>
-  <si>
-    <t>Structure of calf of leg (body structure)</t>
-  </si>
-  <si>
-    <t>722115008</t>
-  </si>
-  <si>
-    <t>Structure of calf of left lower leg (body structure)</t>
-  </si>
-  <si>
-    <t>722116009</t>
-  </si>
-  <si>
-    <t>Structure of calf of right lower leg (body structure)</t>
-  </si>
-  <si>
-    <t>69105007</t>
-  </si>
-  <si>
-    <t>Carotid artery structure (body structure)</t>
-  </si>
-  <si>
-    <t>721028001</t>
-  </si>
-  <si>
-    <t>Structure of left carotid artery (body structure)</t>
-  </si>
-  <si>
-    <t>721033002</t>
-  </si>
-  <si>
-    <t>Structure of right carotid artery (body structure)</t>
-  </si>
-  <si>
-    <t>276885007</t>
-  </si>
-  <si>
-    <t>Core body temperature (observable entity)</t>
-  </si>
-  <si>
-    <t>86547008</t>
-  </si>
-  <si>
-    <t>Structure of dorsalis pedis artery (body structure)</t>
-  </si>
-  <si>
-    <t>792817008</t>
-  </si>
-  <si>
-    <t>Structure of left dorsalis pedis artery (body structure)</t>
-  </si>
-  <si>
-    <t>792816004</t>
-  </si>
-  <si>
-    <t>Structure of right dorsalis pedis artery (body structure)</t>
-  </si>
-  <si>
-    <t>7657000</t>
-  </si>
-  <si>
-    <t>Structure of femoral artery (body structure)</t>
-  </si>
-  <si>
-    <t>113270003</t>
-  </si>
-  <si>
-    <t>Structure of left femoral artery (body structure)</t>
-  </si>
-  <si>
-    <t>69833005</t>
-  </si>
-  <si>
-    <t>Structure of right femoral artery (body structure)</t>
-  </si>
-  <si>
-    <t>69536005</t>
-  </si>
-  <si>
-    <t>Head structure (body structure)</t>
-  </si>
-  <si>
-    <t>29836001</t>
-  </si>
-  <si>
-    <t>Hip region structure (body structure)</t>
-  </si>
-  <si>
-    <t>287679003</t>
-  </si>
-  <si>
-    <t>Left hip region structure (body structure)</t>
-  </si>
-  <si>
-    <t>287579007</t>
-  </si>
-  <si>
-    <t>Right hip region structure (body structure)</t>
-  </si>
-  <si>
-    <t>72696002</t>
-  </si>
-  <si>
-    <t>Knee region structure (body structure)</t>
-  </si>
-  <si>
-    <t>82169009</t>
-  </si>
-  <si>
-    <t>Structure of left knee region (body structure)</t>
-  </si>
-  <si>
-    <t>6757004</t>
-  </si>
-  <si>
-    <t>Structure of right knee region (body structure)</t>
-  </si>
-  <si>
-    <t>80768000</t>
-  </si>
-  <si>
-    <t>Structure of left upper limb (body structure)</t>
-  </si>
-  <si>
-    <t>32153003</t>
-  </si>
-  <si>
-    <t>Structure of left lower limb (body structure)</t>
-  </si>
-  <si>
-    <t>14975008</t>
-  </si>
-  <si>
-    <t>Forearm structure (body structure)</t>
-  </si>
-  <si>
-    <t>66480008</t>
-  </si>
-  <si>
-    <t>Structure of left forearm (body structure)</t>
-  </si>
-  <si>
-    <t>64262003</t>
-  </si>
-  <si>
-    <t>Structure of right forearm (body structure)</t>
-  </si>
-  <si>
-    <t>45048000</t>
-  </si>
-  <si>
-    <t>Neck structure (body structure)</t>
-  </si>
-  <si>
-    <t>123851003</t>
-  </si>
-  <si>
-    <t>Mouth region structure (body structure)</t>
-  </si>
-  <si>
     <t>43899006</t>
   </si>
   <si>
@@ -414,7 +421,7 @@
     <t>68367000</t>
   </si>
   <si>
-    <t>Thigh structure (body structure)</t>
+    <t>Thigh structure (body structure`)</t>
   </si>
   <si>
     <t>61396006</t>
@@ -771,7 +778,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1327,15 +1334,23 @@
         <v>162</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>164</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFVitalsBodySite.xlsx
+++ b/docs/ValueSet-VSVFVitalsBodySite.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
